--- a/stufe-6/quest/PTDATA-2023-migrate-ig/ISiK-Basis/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-6/quest/PTDATA-2023-migrate-ig/ISiK-Basis/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T13:44:45+00:00</t>
+    <t>2026-02-03T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
